--- a/liaisons_Super_Constellation/Reseau_Luxair_L1049_sourced.xlsx
+++ b/liaisons_Super_Constellation/Reseau_Luxair_L1049_sourced.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Réseau Européen (illustratif)" sheetId="1" r:id="rId1"/>
+    <sheet name="Ligne Starliner" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:J10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,122 +416,152 @@
         <v>Escale 1 (Arr. / Dép.)</v>
       </c>
       <c r="F1" t="str">
+        <v>Escale 2 (Arr. / Dép.)</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Escale 3 (Arr. / Dép.)</v>
+      </c>
+      <c r="H1" t="str">
         <v>Destination</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>Arrivée (HL)</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>Fréquence / Note</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LG 201</v>
+        <v>LG 401</v>
       </c>
       <c r="B2" t="str">
-        <v>Ligne de Paris</v>
+        <v>Luxembourg – Johannesburg</v>
       </c>
       <c r="C2" t="str">
         <v>Luxembourg (LUX)</v>
       </c>
       <c r="D2" t="str">
-        <v>08:00</v>
+        <v>20:00</v>
       </c>
       <c r="E2" t="str">
-        <v>Paris (ORY) (09:15 / 10:00)</v>
+        <v>Athènes (23:00 / 00:15 *)</v>
       </c>
       <c r="F2" t="str">
-        <v>Nice</v>
+        <v>Khartoum (04:15 * / 05:15 *)</v>
       </c>
       <c r="G2" t="str">
-        <v>11:30</v>
+        <v>Nairobi (09:15 * / 10:15 *)</v>
       </c>
       <c r="H2" t="str">
-        <v>Quotidien</v>
+        <v>Johannesburg (JNB)</v>
+      </c>
+      <c r="I2" t="str">
+        <v>14:15 *</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Mercredi</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LG 202</v>
+        <v>LG 402</v>
       </c>
       <c r="B3" t="str">
-        <v>Ligne de Paris (Retour)</v>
+        <v>Luxembourg – Johannesburg (Retour)</v>
       </c>
       <c r="C3" t="str">
-        <v>Nice</v>
+        <v>Johannesburg (JNB)</v>
       </c>
       <c r="D3" t="str">
-        <v>17:00</v>
+        <v>18:00</v>
       </c>
       <c r="E3" t="str">
-        <v>Paris (ORY) (18:30 / 19:15)</v>
+        <v>Nairobi (22:00 / 23:00)</v>
       </c>
       <c r="F3" t="str">
+        <v>Khartoum (03:00 * / 04:00 *)</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Athènes (08:00 * / 09:15 *)</v>
+      </c>
+      <c r="H3" t="str">
         <v>Luxembourg (LUX)</v>
       </c>
-      <c r="G3" t="str">
-        <v>20:30</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Quotidien</v>
+      <c r="I3" t="str">
+        <v>12:15 *</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Vendredi</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>LG 301</v>
+        <v/>
       </c>
       <c r="B4" t="str">
-        <v>Ligne du Sud</v>
+        <v/>
       </c>
       <c r="C4" t="str">
-        <v>Luxembourg (LUX)</v>
+        <v/>
       </c>
       <c r="D4" t="str">
-        <v>09:00</v>
+        <v/>
       </c>
       <c r="E4" t="str">
-        <v>Munich (10:30 / 11:15)</v>
+        <v/>
       </c>
       <c r="F4" t="str">
-        <v>Rome</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>13:15</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Mardi, Jeudi, Samedi</v>
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>LG 302</v>
+        <v>Notes :</v>
       </c>
       <c r="B5" t="str">
-        <v>Ligne du Sud (Retour)</v>
+        <v/>
       </c>
       <c r="C5" t="str">
-        <v>Rome</v>
+        <v/>
       </c>
       <c r="D5" t="str">
-        <v>15:00</v>
+        <v/>
       </c>
       <c r="E5" t="str">
-        <v>Munich (17:00 / 17:45)</v>
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v>Luxembourg (LUX)</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>19:15</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>Mercredi, Vendredi, Dimanche</v>
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v/>
+        <v>Sources : la Luxair (fondée en 1962) n'a exploité NI DC-4 NI DC-6, mais a mis en ligne 3 Lockheed L-1649A Starliner — dernier de la lignée Constellation — sur Luxembourg–Johannesburg avec Trek Airways (1964-1969).</v>
       </c>
       <c r="B6" t="str">
         <v/>
@@ -552,12 +582,18 @@
         <v/>
       </c>
       <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Notes :</v>
+        <v>Ligne exploitée en Lockheed L-1649A Starliner (famille Constellation) ; proposée ici pour le L-1049 Super Constellation, son proche parent.</v>
       </c>
       <c r="B7" t="str">
         <v/>
@@ -578,12 +614,18 @@
         <v/>
       </c>
       <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ATTENTION : la Luxair a été fondée en 1962 (Fokker F27, Viscount, Caravelle) — bien après l'ère du L-1049, qu'elle n'a jamais exploité. Feuillet illustratif, ENTIÈREMENT RECONSTITUÉ [R].</v>
+        <v>[R] Reconstitué : numéros de vol et horaires — non issus d'un timetable original.</v>
       </c>
       <c r="B8" t="str">
         <v/>
@@ -604,12 +646,18 @@
         <v/>
       </c>
       <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>[S] Sourcé : uniquement les villes réelles desservies par Luxair — pas l'appareil ni l'époque.</v>
+        <v>* Arrivée un jour plus tard (chaque * = +1 jour). [Tech] = escale technique. HL : Heure locale.</v>
       </c>
       <c r="B9" t="str">
         <v/>
@@ -630,12 +678,18 @@
         <v/>
       </c>
       <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>* Arrivée un jour plus tard (chaque * = +1 jour). [Tech] = escale technique. HL : Heure locale.</v>
+        <v>[R] Vols retour reconstitués par itinéraire miroir (horaires plausibles).</v>
       </c>
       <c r="B10" t="str">
         <v/>
@@ -658,36 +712,16 @@
       <c r="H10" t="str">
         <v/>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>[R] Vols retour reconstitués par itinéraire miroir (horaires plausibles).</v>
-      </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J10"/>
   </ignoredErrors>
 </worksheet>
 </file>